--- a/ScrumReport-Team3-18.3.xlsx
+++ b/ScrumReport-Team3-18.3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\307426\Downloads\UST_Assignments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B611A5F-239A-49F7-8BC1-62F4ED1B7C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFA05545-9104-46FC-8397-B1DEC9603EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="202">
   <si>
     <t>Batch</t>
   </si>
@@ -586,6 +586,66 @@
   </si>
   <si>
     <t>Studied Kubernetes volumes including EmptyDir and HostPath. Learned about static and dynamic provisioning using PV, PVC, and StorageClasses. Implemented storage for MongoDB application and explored NFS for shared storage. Also analyzed OOM errors using shell scripting.</t>
+  </si>
+  <si>
+    <t>Sprint 12</t>
+  </si>
+  <si>
+    <t>Sprint 13</t>
+  </si>
+  <si>
+    <t>T11-001</t>
+  </si>
+  <si>
+    <t>T11-002</t>
+  </si>
+  <si>
+    <t>T11-003</t>
+  </si>
+  <si>
+    <t>T11-004</t>
+  </si>
+  <si>
+    <t>T11-005</t>
+  </si>
+  <si>
+    <t>T11-006</t>
+  </si>
+  <si>
+    <t>T12-001</t>
+  </si>
+  <si>
+    <t>T12-002</t>
+  </si>
+  <si>
+    <t>T12-003</t>
+  </si>
+  <si>
+    <t>T12-004</t>
+  </si>
+  <si>
+    <t>T12-005</t>
+  </si>
+  <si>
+    <t>T12-006</t>
+  </si>
+  <si>
+    <t>T13-001</t>
+  </si>
+  <si>
+    <t>T13-002</t>
+  </si>
+  <si>
+    <t>T13-003</t>
+  </si>
+  <si>
+    <t>T13-004</t>
+  </si>
+  <si>
+    <t>T13-005</t>
+  </si>
+  <si>
+    <t>T13-006</t>
   </si>
 </sst>
 </file>
@@ -690,7 +750,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -725,6 +785,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3511,8 +3572,8 @@
     <col min="1" max="1" width="13.1796875" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" customWidth="1"/>
     <col min="3" max="3" width="17.1796875" customWidth="1"/>
-    <col min="4" max="4" width="130.453125" customWidth="1"/>
-    <col min="5" max="5" width="16.54296875" customWidth="1"/>
+    <col min="4" max="4" width="215.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.54296875" customWidth="1"/>
     <col min="7" max="7" width="13.1796875" customWidth="1"/>
     <col min="8" max="8" width="41.54296875" customWidth="1"/>
@@ -5291,30 +5352,484 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73">
+        <v>8</v>
+      </c>
+      <c r="G73" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F74">
+        <v>8</v>
+      </c>
+      <c r="G74" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75">
+        <v>8</v>
+      </c>
+      <c r="G75" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76">
+        <v>8</v>
+      </c>
+      <c r="G76" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77">
+        <v>8</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78">
+        <v>8</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H79" s="4"/>
+    </row>
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80">
+        <v>6</v>
+      </c>
+      <c r="G80" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81">
+        <v>6</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F82">
+        <v>6</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83">
+        <v>6</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F84">
+        <v>6</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85">
+        <v>6</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H86" s="4"/>
+    </row>
+    <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F87">
+        <v>7</v>
+      </c>
+      <c r="G87" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="D88" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88">
+        <v>7</v>
+      </c>
+      <c r="G88" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89">
+        <v>7</v>
+      </c>
+      <c r="G89" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90">
+        <v>7</v>
+      </c>
+      <c r="G90" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91">
+        <v>7</v>
+      </c>
+      <c r="G91" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92">
+        <v>7</v>
+      </c>
+      <c r="G92" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="97" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="98" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="99" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
